--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R2168b164440747b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Rf805fd5f80e44705"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -9434,7 +9434,39 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="294">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">MapItEasy</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/MapItEasy</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/MapItEasy/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/phongnguyend/MapItEasy/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Audit</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-09-10T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:F293"/>
+  <x:autoFilter ref="A1:F294"/>
 </x:worksheet>
 </file>
--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Rf805fd5f80e44705"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R8fa7598f0d884c2c"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R8fa7598f0d884c2c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Rb3ca4fc0f4284e7d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -9457,7 +9457,7 @@
       </x:c>
       <x:c r="E" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Audit</x:t>
+          <x:t xml:space="preserve">Mapper</x:t>
         </x:is>
       </x:c>
       <x:c r="F" s="4" t="inlineStr">
@@ -9466,7 +9466,39 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="295">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Slang.Net</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Slang.Net</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/Slang.Net/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/egorozh/Slang.NET/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">FilesToCode</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-09-11T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:F294"/>
+  <x:autoFilter ref="A1:F295"/>
 </x:worksheet>
 </file>
--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Rb3ca4fc0f4284e7d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R5bdfa111aba14ff9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -9498,7 +9498,39 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="296">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Forged</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Forged</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/Forged/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/Atulin/Forged</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Tests</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-09-12T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:F295"/>
+  <x:autoFilter ref="A1:F296"/>
 </x:worksheet>
 </file>